--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260630.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260630.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>18.34%</t>
+          <t>18.03%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.38%</t>
+          <t>7.15%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>6.64%</t>
         </is>
       </c>
     </row>
@@ -682,51 +682,51 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.25%</t>
+          <t>5.56%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>38,800,000</t>
+          <t>3,380,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.73%</t>
+          <t>4.95%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>3,250,000</t>
+          <t>38,800,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.48%</t>
+          <t>4.67%</t>
         </is>
       </c>
     </row>
@@ -743,56 +743,56 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>1,350,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.41%</t>
+          <t>3.75%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>940,000</t>
+          <t>1,435,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.53%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>1,435,000</t>
+          <t>940,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>3.32%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
@@ -880,139 +880,139 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.12%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>2,900,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>4,500,000</t>
+          <t>2,750,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>830,000</t>
+          <t>3,217,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1,240,000</t>
+          <t>1,700,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>1,700,000</t>
+          <t>830,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>1,240,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
@@ -1034,51 +1034,51 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>9,911,000</t>
+          <t>450,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>450,000</t>
+          <t>9,911,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -1166,51 +1166,51 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>7,550,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>7,550,000</t>
+          <t>1,950,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
@@ -1232,29 +1232,29 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,950,000</t>
+          <t>450,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
@@ -1283,61 +1283,61 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>450,000</t>
+          <t>795,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>795,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>166,000</t>
+          <t>1,010,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,100 +1547,100 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,010,000</t>
+          <t>166,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>450,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>450,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>5,017,169,026</t>
+          <t>5,358,718,385</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,430,785,282</t>
+          <t>1,484,118,663</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
